--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101884</v>
+        <v>120101885</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,12 +713,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -763,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -923,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101885</v>
+        <v>120101884</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +934,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,11 +960,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101885</v>
+        <v>120101884</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>5189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +713,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -762,7 +763,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +773,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101888</v>
+        <v>120101889</v>
       </c>
       <c r="B3" t="n">
         <v>91863</v>
@@ -834,14 +835,10 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -885,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101884</v>
+        <v>120101885</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,12 +957,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1010,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101889</v>
+        <v>120101885</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,30 +816,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -882,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101885</v>
+        <v>120101888</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>91863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,13 +962,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101888</v>
+        <v>120101891</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,25 +936,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,12 +962,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1010,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101891</v>
+        <v>120101888</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,9 +1082,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101891</v>
+        <v>120101888</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,25 +936,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,9 +962,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1007,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101888</v>
+        <v>120101891</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1082,12 +1085,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101884</v>
+        <v>120101888</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,14 +713,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -763,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101885</v>
+        <v>120101884</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>5189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,20 +810,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,11 +836,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -887,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101888</v>
+        <v>120101885</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,12 +961,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
         <v>120101891</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101888</v>
+        <v>120101889</v>
       </c>
       <c r="B2" t="n">
         <v>91881</v>
@@ -710,14 +710,10 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -761,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101884</v>
+        <v>120101891</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,11 +835,6 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -886,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101885</v>
+        <v>120101884</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +926,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,11 +952,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101891</v>
+        <v>120101885</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1051,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,9 +1077,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101889</v>
+        <v>120101888</v>
       </c>
       <c r="B2" t="n">
         <v>91881</v>
@@ -710,10 +710,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -757,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101891</v>
+        <v>120101885</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +810,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,9 +836,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1039,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101885</v>
+        <v>120101891</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1077,13 +1085,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1126,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101885</v>
+        <v>120101891</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,25 +810,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,13 +836,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -885,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1047,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101891</v>
+        <v>120101885</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1055,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,9 +1081,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101888</v>
+        <v>120101889</v>
       </c>
       <c r="B2" t="n">
         <v>91881</v>
@@ -710,14 +710,10 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -761,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101891</v>
+        <v>120101885</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,9 +832,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101885</v>
+        <v>120101891</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,25 +1055,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1081,13 +1081,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101889</v>
+        <v>120101891</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101885</v>
+        <v>120101889</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,35 +811,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -881,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1043,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101891</v>
+        <v>120101885</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,25 +1051,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1081,9 +1077,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37372-2024 artfynd.xlsx
+++ b/artfynd/A 37372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101891</v>
+        <v>120101888</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -758,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101889</v>
+        <v>120101891</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +810,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
